--- a/Sets-vervestacks.xlsx
+++ b/Sets-vervestacks.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VS_UoG_IE_UK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VS_UoG_IE_UK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65F0607-4D28-4B32-AE51-DDE57479C768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BF23FC-8FE1-42B1-8050-076C1206D86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="3" xr2:uid="{9C81C662-3457-4886-B336-AE2ED9EEB725}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{9C81C662-3457-4886-B336-AE2ED9EEB725}"/>
   </bookViews>
   <sheets>
     <sheet name="geo_sets_GBR" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="456">
   <si>
     <t>VERVESTACKS - the open USE platform · Powered by data · Shaped by vision · Guided by intuition · Fueled by passion</t>
   </si>
@@ -1140,6 +1140,276 @@
   </si>
   <si>
     <t>coal</t>
+  </si>
+  <si>
+    <t>ELE</t>
+  </si>
+  <si>
+    <t>EP_GAS-CC*,EP_OIL-CC*,*gas_cc*,*gas_comb*,*ember</t>
+  </si>
+  <si>
+    <t>gas,elcnga,elcgas,oil,elco</t>
+  </si>
+  <si>
+    <t>CCGT</t>
+  </si>
+  <si>
+    <t>Combined Cycle Gas Turbine</t>
+  </si>
+  <si>
+    <t>Ramp ~8%/min</t>
+  </si>
+  <si>
+    <t>EP_GAS-GT*,EP_OIL-GT*,*gas_turbine*,EN*CT*</t>
+  </si>
+  <si>
+    <t>OCGT</t>
+  </si>
+  <si>
+    <t>Open Cycle Gas Turbine (Peaker)</t>
+  </si>
+  <si>
+    <t>Ramp ~15%/min</t>
+  </si>
+  <si>
+    <t>EP_GAS-ST*,EP_OIL-ST*,*steam*</t>
+  </si>
+  <si>
+    <t>Gas_Oil_Steam</t>
+  </si>
+  <si>
+    <t>Gas/Oil Steam Turbine</t>
+  </si>
+  <si>
+    <t>EP_GAS-IC*,EP_OIL-IC*,*gas_engine*,*internal_comb*</t>
+  </si>
+  <si>
+    <t>Int_Comb</t>
+  </si>
+  <si>
+    <t>Internal Combustion Engine</t>
+  </si>
+  <si>
+    <t>EP_COA-ST*,EP_LIG-ST*,*-CFB*,*coal_subcritical*</t>
+  </si>
+  <si>
+    <t>coal,elcco*</t>
+  </si>
+  <si>
+    <t>Subcrit_Coal</t>
+  </si>
+  <si>
+    <t>Subcritical Coal</t>
+  </si>
+  <si>
+    <t>Ramp ~3%/min</t>
+  </si>
+  <si>
+    <t>EP_COA-SC*,EP_COA-USC*,EP_LIG-SC*,EP_LIG-USC*,*critical*</t>
+  </si>
+  <si>
+    <t>Supercrit_Coal</t>
+  </si>
+  <si>
+    <t>Supercritical/Ultra-Supercritical Coal</t>
+  </si>
+  <si>
+    <t>Ramp ~4%/min</t>
+  </si>
+  <si>
+    <t>*-IGCC*,*coal_igcc*</t>
+  </si>
+  <si>
+    <t>IGCC</t>
+  </si>
+  <si>
+    <t>Integrated Gasification CC</t>
+  </si>
+  <si>
+    <t>CHP</t>
+  </si>
+  <si>
+    <t>CHP_Gas</t>
+  </si>
+  <si>
+    <t>Gas/Oil CHP</t>
+  </si>
+  <si>
+    <t>Same ramp as ELE counterpart</t>
+  </si>
+  <si>
+    <t>CHP_Coal</t>
+  </si>
+  <si>
+    <t>Coal CHP</t>
+  </si>
+  <si>
+    <t>bio*,elcb*</t>
+  </si>
+  <si>
+    <t>CHP_Bio</t>
+  </si>
+  <si>
+    <t>Biomass CHP</t>
+  </si>
+  <si>
+    <t>HPL</t>
+  </si>
+  <si>
+    <t>HOP_Gas</t>
+  </si>
+  <si>
+    <t>Gas/Oil Heat-Only Boiler</t>
+  </si>
+  <si>
+    <t>HOP_Bio</t>
+  </si>
+  <si>
+    <t>Biomass Heat-Only Boiler</t>
+  </si>
+  <si>
+    <t>-*HP*</t>
+  </si>
+  <si>
+    <t>elc,e[_]*</t>
+  </si>
+  <si>
+    <t>HOP_Elec</t>
+  </si>
+  <si>
+    <t>Electric Boiler (DH)</t>
+  </si>
+  <si>
+    <t>*HP*</t>
+  </si>
+  <si>
+    <t>Heat_Pump</t>
+  </si>
+  <si>
+    <t>Large-Scale Heat Pump</t>
+  </si>
+  <si>
+    <t>Bio_Power</t>
+  </si>
+  <si>
+    <t>Biomass Power (ELE)</t>
+  </si>
+  <si>
+    <t>ELE,CHP</t>
+  </si>
+  <si>
+    <t>elcs*,solar</t>
+  </si>
+  <si>
+    <t>Solar_Util</t>
+  </si>
+  <si>
+    <t>Solar Utility</t>
+  </si>
+  <si>
+    <t>elcwin,windon</t>
+  </si>
+  <si>
+    <t>Wind_Onshore</t>
+  </si>
+  <si>
+    <t>Wind Onshore</t>
+  </si>
+  <si>
+    <t>windoff</t>
+  </si>
+  <si>
+    <t>Wind_Offshore</t>
+  </si>
+  <si>
+    <t>Wind Offshore</t>
+  </si>
+  <si>
+    <t>elcgeo,geothermal</t>
+  </si>
+  <si>
+    <t>Geothermal</t>
+  </si>
+  <si>
+    <t>Geothermal Power</t>
+  </si>
+  <si>
+    <t>-*ror*</t>
+  </si>
+  <si>
+    <t>elchyd,hydro</t>
+  </si>
+  <si>
+    <t>Hydro_Dam</t>
+  </si>
+  <si>
+    <t>Hydro Dam</t>
+  </si>
+  <si>
+    <t>And</t>
+  </si>
+  <si>
+    <t>Or</t>
+  </si>
+  <si>
+    <t>*HYD-ROR*,*ror*</t>
+  </si>
+  <si>
+    <t>Hydro_RoR</t>
+  </si>
+  <si>
+    <t>Hydro Run-of-River</t>
+  </si>
+  <si>
+    <t>-*SMR*</t>
+  </si>
+  <si>
+    <t>elcnuc,nuclear</t>
+  </si>
+  <si>
+    <t>Nuclear_P</t>
+  </si>
+  <si>
+    <t>Nuclear (Conventional)</t>
+  </si>
+  <si>
+    <t>*SMR*</t>
+  </si>
+  <si>
+    <t>Nuclear_SMR</t>
+  </si>
+  <si>
+    <t>Nuclear SMR</t>
+  </si>
+  <si>
+    <t>STG</t>
+  </si>
+  <si>
+    <t>*HPS*,*hydro_ps*</t>
+  </si>
+  <si>
+    <t>Hydro_PS</t>
+  </si>
+  <si>
+    <t>Pumped Hydro Storage</t>
+  </si>
+  <si>
+    <t>*4h*,*8h*,*12h*,-*EV*</t>
+  </si>
+  <si>
+    <t>Batt_Util</t>
+  </si>
+  <si>
+    <t>Utility Battery Storage</t>
+  </si>
+  <si>
+    <t>*EV*</t>
+  </si>
+  <si>
+    <t>Batt_EV</t>
+  </si>
+  <si>
+    <t>EV Battery</t>
   </si>
 </sst>
 </file>
@@ -1292,18 +1562,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Heading 2 2" xfId="2" xr:uid="{DEA9101B-31A2-4385-AC01-A9A69B2224F5}"/>
@@ -1759,16 +2030,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="9" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
@@ -3209,16 +3480,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
     </row>
     <row r="9" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
@@ -4098,7 +4369,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA457248-EB36-4093-B59F-7A2515D12AB7}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="86" bestFit="1" customWidth="1"/>
@@ -4109,39 +4380,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>311</v>
       </c>
     </row>
@@ -4206,7 +4477,7 @@
       <c r="B9" t="s">
         <v>360</v>
       </c>
-      <c r="F9" s="8" t="str">
+      <c r="F9" s="7" t="str">
         <f>LEFT(B9,9)</f>
         <v>distr_sol</v>
       </c>
@@ -4215,7 +4486,7 @@
       <c r="B10" t="s">
         <v>361</v>
       </c>
-      <c r="F10" s="8" t="str">
+      <c r="F10" s="7" t="str">
         <f t="shared" ref="F10:F11" si="0">LEFT(B10,9)</f>
         <v>distr_won</v>
       </c>
@@ -4224,7 +4495,7 @@
       <c r="B11" t="s">
         <v>362</v>
       </c>
-      <c r="F11" s="8" t="str">
+      <c r="F11" s="7" t="str">
         <f t="shared" si="0"/>
         <v>distr_wof</v>
       </c>
@@ -4233,7 +4504,7 @@
       <c r="D12" t="s">
         <v>363</v>
       </c>
-      <c r="F12" s="8" t="str">
+      <c r="F12" s="7" t="str">
         <f>"hs_"&amp;D12</f>
         <v>hs_geothermal</v>
       </c>
@@ -4242,7 +4513,7 @@
       <c r="D13" t="s">
         <v>364</v>
       </c>
-      <c r="F13" s="8" t="str">
+      <c r="F13" s="7" t="str">
         <f t="shared" ref="F13:F15" si="1">"hs_"&amp;D13</f>
         <v>hs_hydro</v>
       </c>
@@ -4251,7 +4522,7 @@
       <c r="D14" t="s">
         <v>322</v>
       </c>
-      <c r="F14" s="8" t="str">
+      <c r="F14" s="7" t="str">
         <f t="shared" si="1"/>
         <v>hs_nuclear</v>
       </c>
@@ -4260,9 +4531,467 @@
       <c r="D15" t="s">
         <v>365</v>
       </c>
-      <c r="F15" s="8" t="str">
+      <c r="F15" s="7" t="str">
         <f t="shared" si="1"/>
         <v>hs_coal</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A20" s="5" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A21" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>366</v>
+      </c>
+      <c r="B22" t="s">
+        <v>367</v>
+      </c>
+      <c r="D22" t="s">
+        <v>368</v>
+      </c>
+      <c r="F22" t="s">
+        <v>369</v>
+      </c>
+      <c r="G22" t="s">
+        <v>370</v>
+      </c>
+      <c r="J22" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>366</v>
+      </c>
+      <c r="B23" t="s">
+        <v>372</v>
+      </c>
+      <c r="D23" t="s">
+        <v>368</v>
+      </c>
+      <c r="F23" t="s">
+        <v>373</v>
+      </c>
+      <c r="G23" t="s">
+        <v>374</v>
+      </c>
+      <c r="J23" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>366</v>
+      </c>
+      <c r="B24" t="s">
+        <v>376</v>
+      </c>
+      <c r="D24" t="s">
+        <v>368</v>
+      </c>
+      <c r="F24" t="s">
+        <v>377</v>
+      </c>
+      <c r="G24" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>366</v>
+      </c>
+      <c r="B25" t="s">
+        <v>379</v>
+      </c>
+      <c r="F25" t="s">
+        <v>380</v>
+      </c>
+      <c r="G25" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>366</v>
+      </c>
+      <c r="B26" t="s">
+        <v>382</v>
+      </c>
+      <c r="D26" t="s">
+        <v>383</v>
+      </c>
+      <c r="F26" t="s">
+        <v>384</v>
+      </c>
+      <c r="G26" t="s">
+        <v>385</v>
+      </c>
+      <c r="J26" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>366</v>
+      </c>
+      <c r="B27" t="s">
+        <v>387</v>
+      </c>
+      <c r="D27" t="s">
+        <v>383</v>
+      </c>
+      <c r="F27" t="s">
+        <v>388</v>
+      </c>
+      <c r="G27" t="s">
+        <v>389</v>
+      </c>
+      <c r="J27" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>366</v>
+      </c>
+      <c r="B28" t="s">
+        <v>391</v>
+      </c>
+      <c r="F28" t="s">
+        <v>392</v>
+      </c>
+      <c r="G28" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>394</v>
+      </c>
+      <c r="D29" t="s">
+        <v>368</v>
+      </c>
+      <c r="F29" t="s">
+        <v>395</v>
+      </c>
+      <c r="G29" t="s">
+        <v>396</v>
+      </c>
+      <c r="J29" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>394</v>
+      </c>
+      <c r="D30" t="s">
+        <v>383</v>
+      </c>
+      <c r="F30" t="s">
+        <v>398</v>
+      </c>
+      <c r="G30" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>394</v>
+      </c>
+      <c r="D31" t="s">
+        <v>400</v>
+      </c>
+      <c r="F31" t="s">
+        <v>401</v>
+      </c>
+      <c r="G31" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>403</v>
+      </c>
+      <c r="D32" t="s">
+        <v>368</v>
+      </c>
+      <c r="F32" t="s">
+        <v>404</v>
+      </c>
+      <c r="G32" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>403</v>
+      </c>
+      <c r="D33" t="s">
+        <v>400</v>
+      </c>
+      <c r="F33" t="s">
+        <v>406</v>
+      </c>
+      <c r="G33" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>403</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="D34" t="s">
+        <v>409</v>
+      </c>
+      <c r="F34" t="s">
+        <v>410</v>
+      </c>
+      <c r="G34" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>403</v>
+      </c>
+      <c r="B35" t="s">
+        <v>412</v>
+      </c>
+      <c r="D35" t="s">
+        <v>409</v>
+      </c>
+      <c r="F35" t="s">
+        <v>413</v>
+      </c>
+      <c r="G35" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>366</v>
+      </c>
+      <c r="D36" t="s">
+        <v>400</v>
+      </c>
+      <c r="F36" t="s">
+        <v>415</v>
+      </c>
+      <c r="G36" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>417</v>
+      </c>
+      <c r="D37" t="s">
+        <v>418</v>
+      </c>
+      <c r="F37" t="s">
+        <v>419</v>
+      </c>
+      <c r="G37" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="D38" t="s">
+        <v>421</v>
+      </c>
+      <c r="F38" t="s">
+        <v>422</v>
+      </c>
+      <c r="G38" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="D39" t="s">
+        <v>424</v>
+      </c>
+      <c r="F39" t="s">
+        <v>425</v>
+      </c>
+      <c r="G39" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="D40" t="s">
+        <v>427</v>
+      </c>
+      <c r="F40" t="s">
+        <v>428</v>
+      </c>
+      <c r="G40" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>366</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="D41" t="s">
+        <v>431</v>
+      </c>
+      <c r="F41" t="s">
+        <v>432</v>
+      </c>
+      <c r="G41" t="s">
+        <v>433</v>
+      </c>
+      <c r="H41" t="s">
+        <v>434</v>
+      </c>
+      <c r="I41" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>366</v>
+      </c>
+      <c r="B42" t="s">
+        <v>436</v>
+      </c>
+      <c r="D42" t="s">
+        <v>431</v>
+      </c>
+      <c r="F42" t="s">
+        <v>437</v>
+      </c>
+      <c r="G42" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>366</v>
+      </c>
+      <c r="B43" t="s">
+        <v>439</v>
+      </c>
+      <c r="D43" t="s">
+        <v>440</v>
+      </c>
+      <c r="F43" t="s">
+        <v>441</v>
+      </c>
+      <c r="G43" t="s">
+        <v>442</v>
+      </c>
+      <c r="H43" t="s">
+        <v>434</v>
+      </c>
+      <c r="I43" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>366</v>
+      </c>
+      <c r="B44" t="s">
+        <v>443</v>
+      </c>
+      <c r="D44" t="s">
+        <v>440</v>
+      </c>
+      <c r="F44" t="s">
+        <v>444</v>
+      </c>
+      <c r="G44" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>446</v>
+      </c>
+      <c r="B45" t="s">
+        <v>447</v>
+      </c>
+      <c r="F45" t="s">
+        <v>448</v>
+      </c>
+      <c r="G45" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>446</v>
+      </c>
+      <c r="B46" t="s">
+        <v>450</v>
+      </c>
+      <c r="F46" t="s">
+        <v>451</v>
+      </c>
+      <c r="G46" t="s">
+        <v>452</v>
+      </c>
+      <c r="H46" t="s">
+        <v>434</v>
+      </c>
+      <c r="I46" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>446</v>
+      </c>
+      <c r="B47" t="s">
+        <v>453</v>
+      </c>
+      <c r="F47" t="s">
+        <v>454</v>
+      </c>
+      <c r="G47" t="s">
+        <v>455</v>
       </c>
     </row>
   </sheetData>
